--- a/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.6.1 Advanced Formulas - IF and ISNUMBER statement working file.xlsx
+++ b/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.6.1 Advanced Formulas - IF and ISNUMBER statement working file.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="28810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/travis/Dropbox/Data Handling in Excel/04 Nested If Statements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rittiv/Documents/GitHub/Projects-Data/1.7. EXCEL  SECTION - Advanced Formulas and Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8B11B4-0E6D-2B49-85CA-88ADCE1C2A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8560" yWindow="4780" windowWidth="25600" windowHeight="14400"/>
+    <workbookView xWindow="25620" yWindow="600" windowWidth="25600" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="marketing_perf" sheetId="6" r:id="rId1"/>
@@ -21,10 +22,21 @@
     <definedName name="MARKETING_PERF">marketing_perf!$A$1:$H$381</definedName>
     <definedName name="UNIQUE_KEYPHRASES">marketing_perf!$A$1:$A$381</definedName>
   </definedNames>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -1263,14 +1275,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="44" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -1843,7 +1855,7 @@
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1851,27 +1863,27 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="20" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="20" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="37" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="37" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1879,21 +1891,19 @@
     <xf numFmtId="0" fontId="20" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="34" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="34" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="1" fillId="35" borderId="0" xfId="48" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="2" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="20" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="20" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="20" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="20" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="20" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="20" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1946,7 +1956,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Percent" xfId="48" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="48" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -1956,6 +1966,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2247,7 +2260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L381"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2261,7 +2274,7 @@
     <col min="9" max="9" width="13.83203125" style="6" customWidth="1"/>
     <col min="10" max="10" width="14.6640625" style="6" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="13.1640625" style="28" customWidth="1"/>
+    <col min="12" max="12" width="13.1640625" style="10" customWidth="1"/>
     <col min="13" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
@@ -2296,7 +2309,7 @@
       <c r="J1" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="27" t="s">
         <v>405</v>
       </c>
       <c r="L1" s="26" t="s">
@@ -2329,19 +2342,19 @@
         <v>5590.04</v>
       </c>
       <c r="I2" s="22">
-        <f>H2/E2</f>
+        <f>IF(E2&gt;0, H2/E2, " ")</f>
         <v>2.0079166666666666</v>
       </c>
       <c r="J2" s="22" t="str">
-        <f>IF(I2&lt;=0.5,"Low",IF(I2&lt;=1.5,"Medium","High"))</f>
+        <f>IF(ISNUMBER(I2), IF(I2&lt;=0.5,"Low",IF(I2&lt;=1.5,"Medium","High")), "Untested ")</f>
         <v>High</v>
       </c>
       <c r="K2" s="24">
-        <f>G2/F2</f>
+        <f>IF(F2&gt;0, G2/F2, " ")</f>
         <v>69.233571428571437</v>
       </c>
-      <c r="L2" s="27" t="str">
-        <f>IF(K2&lt;=75,"Low",IF(K2&lt;=200,"Medium","High"))</f>
+      <c r="L2" s="24" t="str">
+        <f>IF(ISNUMBER(K2), IF(K2&lt;=75,"Low",IF(K2&lt;=200,"Medium","High")), "Untested")</f>
         <v>Low</v>
       </c>
     </row>
@@ -2371,19 +2384,19 @@
         <v>3410.27</v>
       </c>
       <c r="I3" s="22">
-        <f t="shared" ref="I3:I66" si="0">H3/E3</f>
+        <f t="shared" ref="I3:I66" si="0">IF(E3&gt;0, H3/E3, " ")</f>
         <v>2.7907283142389527</v>
       </c>
       <c r="J3" s="22" t="str">
-        <f t="shared" ref="J3:J66" si="1">IF(I3&lt;=0.5,"Low",IF(I3&lt;=1.5,"Medium","High"))</f>
+        <f t="shared" ref="J3:J66" si="1">IF(ISNUMBER(I3), IF(I3&lt;=0.5,"Low",IF(I3&lt;=1.5,"Medium","High")), "UNTESTED ")</f>
         <v>High</v>
       </c>
       <c r="K3" s="24">
-        <f t="shared" ref="K3:K66" si="2">G3/F3</f>
+        <f t="shared" ref="K3:K66" si="2">IF(F3&gt;0, G3/F3, " ")</f>
         <v>67.735749999999996</v>
       </c>
-      <c r="L3" s="27" t="str">
-        <f t="shared" ref="L3:L66" si="3">IF(K3&lt;=75,"Low",IF(K3&lt;=200,"Medium","High"))</f>
+      <c r="L3" s="24" t="str">
+        <f t="shared" ref="L3:L66" si="3">IF(ISNUMBER(K3), IF(K3&lt;=75,"Low",IF(K3&lt;=200,"Medium","High")), "Untested")</f>
         <v>Low</v>
       </c>
     </row>
@@ -2424,7 +2437,7 @@
         <f t="shared" si="2"/>
         <v>87.451111111111103</v>
       </c>
-      <c r="L4" s="27" t="str">
+      <c r="L4" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -2466,7 +2479,7 @@
         <f t="shared" si="2"/>
         <v>57.843333333333334</v>
       </c>
-      <c r="L5" s="27" t="str">
+      <c r="L5" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -2508,7 +2521,7 @@
         <f t="shared" si="2"/>
         <v>80.88277777777779</v>
       </c>
-      <c r="L6" s="27" t="str">
+      <c r="L6" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -2550,7 +2563,7 @@
         <f t="shared" si="2"/>
         <v>98.569285714285712</v>
       </c>
-      <c r="L7" s="27" t="str">
+      <c r="L7" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -2592,7 +2605,7 @@
         <f t="shared" si="2"/>
         <v>239.92</v>
       </c>
-      <c r="L8" s="27" t="str">
+      <c r="L8" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -2634,7 +2647,7 @@
         <f t="shared" si="2"/>
         <v>106.47909090909091</v>
       </c>
-      <c r="L9" s="27" t="str">
+      <c r="L9" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -2676,7 +2689,7 @@
         <f t="shared" si="2"/>
         <v>66.023750000000007</v>
       </c>
-      <c r="L10" s="27" t="str">
+      <c r="L10" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -2718,7 +2731,7 @@
         <f t="shared" si="2"/>
         <v>87.818181818181813</v>
       </c>
-      <c r="L11" s="27" t="str">
+      <c r="L11" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -2760,7 +2773,7 @@
         <f t="shared" si="2"/>
         <v>218.75</v>
       </c>
-      <c r="L12" s="27" t="str">
+      <c r="L12" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -2802,7 +2815,7 @@
         <f t="shared" si="2"/>
         <v>164.4</v>
       </c>
-      <c r="L13" s="27" t="str">
+      <c r="L13" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -2844,7 +2857,7 @@
         <f t="shared" si="2"/>
         <v>53.346000000000004</v>
       </c>
-      <c r="L14" s="27" t="str">
+      <c r="L14" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -2886,7 +2899,7 @@
         <f t="shared" si="2"/>
         <v>720</v>
       </c>
-      <c r="L15" s="27" t="str">
+      <c r="L15" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -2928,7 +2941,7 @@
         <f t="shared" si="2"/>
         <v>79.734444444444449</v>
       </c>
-      <c r="L16" s="27" t="str">
+      <c r="L16" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -2970,7 +2983,7 @@
         <f t="shared" si="2"/>
         <v>88.737499999999997</v>
       </c>
-      <c r="L17" s="27" t="str">
+      <c r="L17" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3012,7 +3025,7 @@
         <f t="shared" si="2"/>
         <v>236.49666666666667</v>
       </c>
-      <c r="L18" s="27" t="str">
+      <c r="L18" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3054,7 +3067,7 @@
         <f t="shared" si="2"/>
         <v>87.185000000000002</v>
       </c>
-      <c r="L19" s="27" t="str">
+      <c r="L19" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3096,7 +3109,7 @@
         <f t="shared" si="2"/>
         <v>105.33333333333333</v>
       </c>
-      <c r="L20" s="27" t="str">
+      <c r="L20" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3138,7 +3151,7 @@
         <f t="shared" si="2"/>
         <v>59.160000000000004</v>
       </c>
-      <c r="L21" s="27" t="str">
+      <c r="L21" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3180,7 +3193,7 @@
         <f t="shared" si="2"/>
         <v>243.5</v>
       </c>
-      <c r="L22" s="27" t="str">
+      <c r="L22" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3222,7 +3235,7 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="L23" s="27" t="str">
+      <c r="L23" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3264,7 +3277,7 @@
         <f t="shared" si="2"/>
         <v>241.35</v>
       </c>
-      <c r="L24" s="27" t="str">
+      <c r="L24" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3306,7 +3319,7 @@
         <f t="shared" si="2"/>
         <v>117.64749999999999</v>
       </c>
-      <c r="L25" s="27" t="str">
+      <c r="L25" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3348,7 +3361,7 @@
         <f t="shared" si="2"/>
         <v>77.971666666666664</v>
       </c>
-      <c r="L26" s="27" t="str">
+      <c r="L26" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3390,7 +3403,7 @@
         <f t="shared" si="2"/>
         <v>229</v>
       </c>
-      <c r="L27" s="27" t="str">
+      <c r="L27" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3432,7 +3445,7 @@
         <f t="shared" si="2"/>
         <v>217.5</v>
       </c>
-      <c r="L28" s="27" t="str">
+      <c r="L28" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3474,7 +3487,7 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="L29" s="27" t="str">
+      <c r="L29" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3516,7 +3529,7 @@
         <f t="shared" si="2"/>
         <v>137.66666666666666</v>
       </c>
-      <c r="L30" s="27" t="str">
+      <c r="L30" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3558,7 +3571,7 @@
         <f t="shared" si="2"/>
         <v>64.583333333333329</v>
       </c>
-      <c r="L31" s="27" t="str">
+      <c r="L31" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3600,7 +3613,7 @@
         <f t="shared" si="2"/>
         <v>96.732500000000002</v>
       </c>
-      <c r="L32" s="27" t="str">
+      <c r="L32" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3642,7 +3655,7 @@
         <f t="shared" si="2"/>
         <v>127.99666666666667</v>
       </c>
-      <c r="L33" s="27" t="str">
+      <c r="L33" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3684,7 +3697,7 @@
         <f t="shared" si="2"/>
         <v>94.49</v>
       </c>
-      <c r="L34" s="27" t="str">
+      <c r="L34" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3726,7 +3739,7 @@
         <f t="shared" si="2"/>
         <v>62.5</v>
       </c>
-      <c r="L35" s="27" t="str">
+      <c r="L35" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3768,7 +3781,7 @@
         <f t="shared" si="2"/>
         <v>92.5</v>
       </c>
-      <c r="L36" s="27" t="str">
+      <c r="L36" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3810,7 +3823,7 @@
         <f t="shared" si="2"/>
         <v>183.5</v>
       </c>
-      <c r="L37" s="27" t="str">
+      <c r="L37" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3852,7 +3865,7 @@
         <f t="shared" si="2"/>
         <v>60.15</v>
       </c>
-      <c r="L38" s="27" t="str">
+      <c r="L38" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3894,7 +3907,7 @@
         <f t="shared" si="2"/>
         <v>58.24666666666667</v>
       </c>
-      <c r="L39" s="27" t="str">
+      <c r="L39" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3936,7 +3949,7 @@
         <f t="shared" si="2"/>
         <v>349</v>
       </c>
-      <c r="L40" s="27" t="str">
+      <c r="L40" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3978,7 +3991,7 @@
         <f t="shared" si="2"/>
         <v>48.042857142857144</v>
       </c>
-      <c r="L41" s="27" t="str">
+      <c r="L41" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4020,7 +4033,7 @@
         <f t="shared" si="2"/>
         <v>166.75</v>
       </c>
-      <c r="L42" s="27" t="str">
+      <c r="L42" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4062,7 +4075,7 @@
         <f t="shared" si="2"/>
         <v>40.712499999999999</v>
       </c>
-      <c r="L43" s="27" t="str">
+      <c r="L43" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4104,7 +4117,7 @@
         <f t="shared" si="2"/>
         <v>78.25</v>
       </c>
-      <c r="L44" s="27" t="str">
+      <c r="L44" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4146,7 +4159,7 @@
         <f t="shared" si="2"/>
         <v>76.872500000000002</v>
       </c>
-      <c r="L45" s="27" t="str">
+      <c r="L45" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4188,7 +4201,7 @@
         <f t="shared" si="2"/>
         <v>149.495</v>
       </c>
-      <c r="L46" s="27" t="str">
+      <c r="L46" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4230,7 +4243,7 @@
         <f t="shared" si="2"/>
         <v>73.547499999999999</v>
       </c>
-      <c r="L47" s="27" t="str">
+      <c r="L47" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4272,7 +4285,7 @@
         <f t="shared" si="2"/>
         <v>92.333333333333329</v>
       </c>
-      <c r="L48" s="27" t="str">
+      <c r="L48" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4314,7 +4327,7 @@
         <f t="shared" si="2"/>
         <v>53.6</v>
       </c>
-      <c r="L49" s="27" t="str">
+      <c r="L49" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4356,7 +4369,7 @@
         <f t="shared" si="2"/>
         <v>66.75</v>
       </c>
-      <c r="L50" s="27" t="str">
+      <c r="L50" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4398,7 +4411,7 @@
         <f t="shared" si="2"/>
         <v>262.5</v>
       </c>
-      <c r="L51" s="27" t="str">
+      <c r="L51" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4440,7 +4453,7 @@
         <f t="shared" si="2"/>
         <v>262</v>
       </c>
-      <c r="L52" s="27" t="str">
+      <c r="L52" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4482,7 +4495,7 @@
         <f t="shared" si="2"/>
         <v>65.424999999999997</v>
       </c>
-      <c r="L53" s="27" t="str">
+      <c r="L53" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4524,7 +4537,7 @@
         <f t="shared" si="2"/>
         <v>260.91000000000003</v>
       </c>
-      <c r="L54" s="27" t="str">
+      <c r="L54" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4566,7 +4579,7 @@
         <f t="shared" si="2"/>
         <v>260</v>
       </c>
-      <c r="L55" s="27" t="str">
+      <c r="L55" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4608,7 +4621,7 @@
         <f t="shared" si="2"/>
         <v>51.9</v>
       </c>
-      <c r="L56" s="27" t="str">
+      <c r="L56" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4650,7 +4663,7 @@
         <f t="shared" si="2"/>
         <v>259</v>
       </c>
-      <c r="L57" s="27" t="str">
+      <c r="L57" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4692,7 +4705,7 @@
         <f t="shared" si="2"/>
         <v>258</v>
       </c>
-      <c r="L58" s="27" t="str">
+      <c r="L58" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4734,7 +4747,7 @@
         <f t="shared" si="2"/>
         <v>250</v>
       </c>
-      <c r="L59" s="27" t="str">
+      <c r="L59" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4776,7 +4789,7 @@
         <f t="shared" si="2"/>
         <v>82.333333333333329</v>
       </c>
-      <c r="L60" s="27" t="str">
+      <c r="L60" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4818,7 +4831,7 @@
         <f t="shared" si="2"/>
         <v>80.833333333333329</v>
       </c>
-      <c r="L61" s="27" t="str">
+      <c r="L61" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4860,7 +4873,7 @@
         <f t="shared" si="2"/>
         <v>59.5</v>
       </c>
-      <c r="L62" s="27" t="str">
+      <c r="L62" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4902,7 +4915,7 @@
         <f t="shared" si="2"/>
         <v>237</v>
       </c>
-      <c r="L63" s="27" t="str">
+      <c r="L63" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4944,7 +4957,7 @@
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="L64" s="27" t="str">
+      <c r="L64" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4986,7 +4999,7 @@
         <f t="shared" si="2"/>
         <v>74.5</v>
       </c>
-      <c r="L65" s="27" t="str">
+      <c r="L65" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -5028,7 +5041,7 @@
         <f t="shared" si="2"/>
         <v>36.718333333333334</v>
       </c>
-      <c r="L66" s="27" t="str">
+      <c r="L66" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -5059,19 +5072,19 @@
         <v>67.88</v>
       </c>
       <c r="I67" s="22">
-        <f t="shared" ref="I67:I130" si="4">H67/E67</f>
+        <f t="shared" ref="I67:I130" si="4">IF(E67&gt;0, H67/E67, " ")</f>
         <v>0.64037735849056598</v>
       </c>
       <c r="J67" s="22" t="str">
-        <f t="shared" ref="J67:J130" si="5">IF(I67&lt;=0.5,"Low",IF(I67&lt;=1.5,"Medium","High"))</f>
+        <f t="shared" ref="J67:J130" si="5">IF(ISNUMBER(I67), IF(I67&lt;=0.5,"Low",IF(I67&lt;=1.5,"Medium","High")), "UNTESTED ")</f>
         <v>Medium</v>
       </c>
       <c r="K67" s="24">
-        <f t="shared" ref="K67:K130" si="6">G67/F67</f>
+        <f t="shared" ref="K67:K130" si="6">IF(F67&gt;0, G67/F67, " ")</f>
         <v>70.8</v>
       </c>
-      <c r="L67" s="27" t="str">
-        <f t="shared" ref="L67:L130" si="7">IF(K67&lt;=75,"Low",IF(K67&lt;=200,"Medium","High"))</f>
+      <c r="L67" s="24" t="str">
+        <f t="shared" ref="L67:L130" si="7">IF(ISNUMBER(K67), IF(K67&lt;=75,"Low",IF(K67&lt;=200,"Medium","High")), "Untested")</f>
         <v>Low</v>
       </c>
     </row>
@@ -5112,7 +5125,7 @@
         <f t="shared" si="6"/>
         <v>70.5</v>
       </c>
-      <c r="L68" s="27" t="str">
+      <c r="L68" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5154,7 +5167,7 @@
         <f t="shared" si="6"/>
         <v>68.526666666666671</v>
       </c>
-      <c r="L69" s="27" t="str">
+      <c r="L69" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5196,7 +5209,7 @@
         <f t="shared" si="6"/>
         <v>101.99</v>
       </c>
-      <c r="L70" s="27" t="str">
+      <c r="L70" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5238,7 +5251,7 @@
         <f t="shared" si="6"/>
         <v>203.6</v>
       </c>
-      <c r="L71" s="27" t="str">
+      <c r="L71" s="24" t="str">
         <f t="shared" si="7"/>
         <v>High</v>
       </c>
@@ -5280,7 +5293,7 @@
         <f t="shared" si="6"/>
         <v>97.5</v>
       </c>
-      <c r="L72" s="27" t="str">
+      <c r="L72" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5322,7 +5335,7 @@
         <f t="shared" si="6"/>
         <v>188</v>
       </c>
-      <c r="L73" s="27" t="str">
+      <c r="L73" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5364,7 +5377,7 @@
         <f t="shared" si="6"/>
         <v>183</v>
       </c>
-      <c r="L74" s="27" t="str">
+      <c r="L74" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5406,7 +5419,7 @@
         <f t="shared" si="6"/>
         <v>88.495000000000005</v>
       </c>
-      <c r="L75" s="27" t="str">
+      <c r="L75" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5448,7 +5461,7 @@
         <f t="shared" si="6"/>
         <v>170</v>
       </c>
-      <c r="L76" s="27" t="str">
+      <c r="L76" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5490,7 +5503,7 @@
         <f t="shared" si="6"/>
         <v>162.9</v>
       </c>
-      <c r="L77" s="27" t="str">
+      <c r="L77" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5532,7 +5545,7 @@
         <f t="shared" si="6"/>
         <v>162</v>
       </c>
-      <c r="L78" s="27" t="str">
+      <c r="L78" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5574,7 +5587,7 @@
         <f t="shared" si="6"/>
         <v>40.15</v>
       </c>
-      <c r="L79" s="27" t="str">
+      <c r="L79" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5616,7 +5629,7 @@
         <f t="shared" si="6"/>
         <v>157</v>
       </c>
-      <c r="L80" s="27" t="str">
+      <c r="L80" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5658,7 +5671,7 @@
         <f t="shared" si="6"/>
         <v>30.75</v>
       </c>
-      <c r="L81" s="27" t="str">
+      <c r="L81" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5700,7 +5713,7 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="L82" s="27" t="str">
+      <c r="L82" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5742,7 +5755,7 @@
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="L83" s="27" t="str">
+      <c r="L83" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5784,7 +5797,7 @@
         <f t="shared" si="6"/>
         <v>74.734999999999999</v>
       </c>
-      <c r="L84" s="27" t="str">
+      <c r="L84" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5826,7 +5839,7 @@
         <f t="shared" si="6"/>
         <v>74.5</v>
       </c>
-      <c r="L85" s="27" t="str">
+      <c r="L85" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5868,7 +5881,7 @@
         <f t="shared" si="6"/>
         <v>71.965000000000003</v>
       </c>
-      <c r="L86" s="27" t="str">
+      <c r="L86" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5910,7 +5923,7 @@
         <f t="shared" si="6"/>
         <v>142</v>
       </c>
-      <c r="L87" s="27" t="str">
+      <c r="L87" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5952,7 +5965,7 @@
         <f t="shared" si="6"/>
         <v>139</v>
       </c>
-      <c r="L88" s="27" t="str">
+      <c r="L88" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5994,7 +6007,7 @@
         <f t="shared" si="6"/>
         <v>134</v>
       </c>
-      <c r="L89" s="27" t="str">
+      <c r="L89" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6036,7 +6049,7 @@
         <f t="shared" si="6"/>
         <v>26.7</v>
       </c>
-      <c r="L90" s="27" t="str">
+      <c r="L90" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6078,7 +6091,7 @@
         <f t="shared" si="6"/>
         <v>132</v>
       </c>
-      <c r="L91" s="27" t="str">
+      <c r="L91" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6120,7 +6133,7 @@
         <f t="shared" si="6"/>
         <v>65.125</v>
       </c>
-      <c r="L92" s="27" t="str">
+      <c r="L92" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6162,7 +6175,7 @@
         <f t="shared" si="6"/>
         <v>43.143333333333338</v>
       </c>
-      <c r="L93" s="27" t="str">
+      <c r="L93" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6204,7 +6217,7 @@
         <f t="shared" si="6"/>
         <v>127.2</v>
       </c>
-      <c r="L94" s="27" t="str">
+      <c r="L94" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6246,7 +6259,7 @@
         <f t="shared" si="6"/>
         <v>62</v>
       </c>
-      <c r="L95" s="27" t="str">
+      <c r="L95" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6288,7 +6301,7 @@
         <f t="shared" si="6"/>
         <v>61.5</v>
       </c>
-      <c r="L96" s="27" t="str">
+      <c r="L96" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6330,7 +6343,7 @@
         <f t="shared" si="6"/>
         <v>58.9</v>
       </c>
-      <c r="L97" s="27" t="str">
+      <c r="L97" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6372,7 +6385,7 @@
         <f t="shared" si="6"/>
         <v>115</v>
       </c>
-      <c r="L98" s="27" t="str">
+      <c r="L98" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6414,7 +6427,7 @@
         <f t="shared" si="6"/>
         <v>113</v>
       </c>
-      <c r="L99" s="27" t="str">
+      <c r="L99" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6456,7 +6469,7 @@
         <f t="shared" si="6"/>
         <v>113</v>
       </c>
-      <c r="L100" s="27" t="str">
+      <c r="L100" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6498,7 +6511,7 @@
         <f t="shared" si="6"/>
         <v>111.6</v>
       </c>
-      <c r="L101" s="27" t="str">
+      <c r="L101" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6540,7 +6553,7 @@
         <f t="shared" si="6"/>
         <v>109</v>
       </c>
-      <c r="L102" s="27" t="str">
+      <c r="L102" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6582,7 +6595,7 @@
         <f t="shared" si="6"/>
         <v>103.5</v>
       </c>
-      <c r="L103" s="27" t="str">
+      <c r="L103" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6624,7 +6637,7 @@
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
-      <c r="L104" s="27" t="str">
+      <c r="L104" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6666,7 +6679,7 @@
         <f t="shared" si="6"/>
         <v>101.5</v>
       </c>
-      <c r="L105" s="27" t="str">
+      <c r="L105" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6708,7 +6721,7 @@
         <f t="shared" si="6"/>
         <v>33.016666666666666</v>
       </c>
-      <c r="L106" s="27" t="str">
+      <c r="L106" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6750,7 +6763,7 @@
         <f t="shared" si="6"/>
         <v>99</v>
       </c>
-      <c r="L107" s="27" t="str">
+      <c r="L107" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6792,7 +6805,7 @@
         <f t="shared" si="6"/>
         <v>99</v>
       </c>
-      <c r="L108" s="27" t="str">
+      <c r="L108" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6834,7 +6847,7 @@
         <f t="shared" si="6"/>
         <v>47.994999999999997</v>
       </c>
-      <c r="L109" s="27" t="str">
+      <c r="L109" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6876,7 +6889,7 @@
         <f t="shared" si="6"/>
         <v>31.99</v>
       </c>
-      <c r="L110" s="27" t="str">
+      <c r="L110" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6918,7 +6931,7 @@
         <f t="shared" si="6"/>
         <v>94</v>
       </c>
-      <c r="L111" s="27" t="str">
+      <c r="L111" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6960,7 +6973,7 @@
         <f t="shared" si="6"/>
         <v>94</v>
       </c>
-      <c r="L112" s="27" t="str">
+      <c r="L112" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7002,7 +7015,7 @@
         <f t="shared" si="6"/>
         <v>46.49</v>
       </c>
-      <c r="L113" s="27" t="str">
+      <c r="L113" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7044,7 +7057,7 @@
         <f t="shared" si="6"/>
         <v>92</v>
       </c>
-      <c r="L114" s="27" t="str">
+      <c r="L114" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7086,7 +7099,7 @@
         <f t="shared" si="6"/>
         <v>92</v>
       </c>
-      <c r="L115" s="27" t="str">
+      <c r="L115" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7128,7 +7141,7 @@
         <f t="shared" si="6"/>
         <v>45.5</v>
       </c>
-      <c r="L116" s="27" t="str">
+      <c r="L116" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7170,7 +7183,7 @@
         <f t="shared" si="6"/>
         <v>45.5</v>
       </c>
-      <c r="L117" s="27" t="str">
+      <c r="L117" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7212,7 +7225,7 @@
         <f t="shared" si="6"/>
         <v>89.98</v>
       </c>
-      <c r="L118" s="27" t="str">
+      <c r="L118" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7254,7 +7267,7 @@
         <f t="shared" si="6"/>
         <v>89.5</v>
       </c>
-      <c r="L119" s="27" t="str">
+      <c r="L119" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7296,7 +7309,7 @@
         <f t="shared" si="6"/>
         <v>88</v>
       </c>
-      <c r="L120" s="27" t="str">
+      <c r="L120" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7338,7 +7351,7 @@
         <f t="shared" si="6"/>
         <v>88</v>
       </c>
-      <c r="L121" s="27" t="str">
+      <c r="L121" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7380,7 +7393,7 @@
         <f t="shared" si="6"/>
         <v>88</v>
       </c>
-      <c r="L122" s="27" t="str">
+      <c r="L122" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7422,7 +7435,7 @@
         <f t="shared" si="6"/>
         <v>87</v>
       </c>
-      <c r="L123" s="27" t="str">
+      <c r="L123" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7464,7 +7477,7 @@
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="L124" s="27" t="str">
+      <c r="L124" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7506,7 +7519,7 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="L125" s="27" t="str">
+      <c r="L125" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7548,7 +7561,7 @@
         <f t="shared" si="6"/>
         <v>85.92</v>
       </c>
-      <c r="L126" s="27" t="str">
+      <c r="L126" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7590,7 +7603,7 @@
         <f t="shared" si="6"/>
         <v>42.825000000000003</v>
       </c>
-      <c r="L127" s="27" t="str">
+      <c r="L127" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7632,7 +7645,7 @@
         <f t="shared" si="6"/>
         <v>84</v>
       </c>
-      <c r="L128" s="27" t="str">
+      <c r="L128" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7674,7 +7687,7 @@
         <f t="shared" si="6"/>
         <v>83</v>
       </c>
-      <c r="L129" s="27" t="str">
+      <c r="L129" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7716,7 +7729,7 @@
         <f t="shared" si="6"/>
         <v>82</v>
       </c>
-      <c r="L130" s="27" t="str">
+      <c r="L130" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7747,19 +7760,19 @@
         <v>14.46</v>
       </c>
       <c r="I131" s="22">
-        <f t="shared" ref="I131:I194" si="8">H131/E131</f>
+        <f t="shared" ref="I131:I194" si="8">IF(E131&gt;0, H131/E131, " ")</f>
         <v>0.30765957446808512</v>
       </c>
       <c r="J131" s="22" t="str">
-        <f t="shared" ref="J131:J194" si="9">IF(I131&lt;=0.5,"Low",IF(I131&lt;=1.5,"Medium","High"))</f>
+        <f t="shared" ref="J131:J194" si="9">IF(ISNUMBER(I131), IF(I131&lt;=0.5,"Low",IF(I131&lt;=1.5,"Medium","High")), "UNTESTED ")</f>
         <v>Low</v>
       </c>
       <c r="K131" s="24">
-        <f t="shared" ref="K131:K194" si="10">G131/F131</f>
+        <f t="shared" ref="K131:K194" si="10">IF(F131&gt;0, G131/F131, " ")</f>
         <v>80</v>
       </c>
-      <c r="L131" s="27" t="str">
-        <f t="shared" ref="L131:L194" si="11">IF(K131&lt;=75,"Low",IF(K131&lt;=200,"Medium","High"))</f>
+      <c r="L131" s="24" t="str">
+        <f t="shared" ref="L131:L194" si="11">IF(ISNUMBER(K131), IF(K131&lt;=75,"Low",IF(K131&lt;=200,"Medium","High")), "Untested")</f>
         <v>Medium</v>
       </c>
     </row>
@@ -7800,7 +7813,7 @@
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="L132" s="27" t="str">
+      <c r="L132" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -7842,7 +7855,7 @@
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="L133" s="27" t="str">
+      <c r="L133" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -7884,7 +7897,7 @@
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="L134" s="27" t="str">
+      <c r="L134" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -7926,7 +7939,7 @@
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="L135" s="27" t="str">
+      <c r="L135" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -7968,7 +7981,7 @@
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="L136" s="27" t="str">
+      <c r="L136" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8010,7 +8023,7 @@
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="L137" s="27" t="str">
+      <c r="L137" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8052,7 +8065,7 @@
         <f t="shared" si="10"/>
         <v>77.5</v>
       </c>
-      <c r="L138" s="27" t="str">
+      <c r="L138" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8094,7 +8107,7 @@
         <f t="shared" si="10"/>
         <v>76</v>
       </c>
-      <c r="L139" s="27" t="str">
+      <c r="L139" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8136,7 +8149,7 @@
         <f t="shared" si="10"/>
         <v>75.98</v>
       </c>
-      <c r="L140" s="27" t="str">
+      <c r="L140" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8178,7 +8191,7 @@
         <f t="shared" si="10"/>
         <v>37.5</v>
       </c>
-      <c r="L141" s="27" t="str">
+      <c r="L141" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8220,7 +8233,7 @@
         <f t="shared" si="10"/>
         <v>75</v>
       </c>
-      <c r="L142" s="27" t="str">
+      <c r="L142" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8262,7 +8275,7 @@
         <f t="shared" si="10"/>
         <v>74</v>
       </c>
-      <c r="L143" s="27" t="str">
+      <c r="L143" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8304,7 +8317,7 @@
         <f t="shared" si="10"/>
         <v>74</v>
       </c>
-      <c r="L144" s="27" t="str">
+      <c r="L144" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8346,7 +8359,7 @@
         <f t="shared" si="10"/>
         <v>37</v>
       </c>
-      <c r="L145" s="27" t="str">
+      <c r="L145" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8388,7 +8401,7 @@
         <f t="shared" si="10"/>
         <v>72.98</v>
       </c>
-      <c r="L146" s="27" t="str">
+      <c r="L146" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8430,7 +8443,7 @@
         <f t="shared" si="10"/>
         <v>69.989999999999995</v>
       </c>
-      <c r="L147" s="27" t="str">
+      <c r="L147" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8472,7 +8485,7 @@
         <f t="shared" si="10"/>
         <v>68</v>
       </c>
-      <c r="L148" s="27" t="str">
+      <c r="L148" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8514,7 +8527,7 @@
         <f t="shared" si="10"/>
         <v>67</v>
       </c>
-      <c r="L149" s="27" t="str">
+      <c r="L149" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8556,7 +8569,7 @@
         <f t="shared" si="10"/>
         <v>64</v>
       </c>
-      <c r="L150" s="27" t="str">
+      <c r="L150" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8598,7 +8611,7 @@
         <f t="shared" si="10"/>
         <v>63.6</v>
       </c>
-      <c r="L151" s="27" t="str">
+      <c r="L151" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8640,7 +8653,7 @@
         <f t="shared" si="10"/>
         <v>63.5</v>
       </c>
-      <c r="L152" s="27" t="str">
+      <c r="L152" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8682,7 +8695,7 @@
         <f t="shared" si="10"/>
         <v>63</v>
       </c>
-      <c r="L153" s="27" t="str">
+      <c r="L153" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8724,7 +8737,7 @@
         <f t="shared" si="10"/>
         <v>63</v>
       </c>
-      <c r="L154" s="27" t="str">
+      <c r="L154" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8766,7 +8779,7 @@
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
-      <c r="L155" s="27" t="str">
+      <c r="L155" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8808,7 +8821,7 @@
         <f t="shared" si="10"/>
         <v>31</v>
       </c>
-      <c r="L156" s="27" t="str">
+      <c r="L156" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8850,7 +8863,7 @@
         <f t="shared" si="10"/>
         <v>20.400000000000002</v>
       </c>
-      <c r="L157" s="27" t="str">
+      <c r="L157" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8892,7 +8905,7 @@
         <f t="shared" si="10"/>
         <v>30.5</v>
       </c>
-      <c r="L158" s="27" t="str">
+      <c r="L158" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8934,7 +8947,7 @@
         <f t="shared" si="10"/>
         <v>61</v>
       </c>
-      <c r="L159" s="27" t="str">
+      <c r="L159" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8976,7 +8989,7 @@
         <f t="shared" si="10"/>
         <v>60</v>
       </c>
-      <c r="L160" s="27" t="str">
+      <c r="L160" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9018,7 +9031,7 @@
         <f t="shared" si="10"/>
         <v>59</v>
       </c>
-      <c r="L161" s="27" t="str">
+      <c r="L161" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9060,7 +9073,7 @@
         <f t="shared" si="10"/>
         <v>58.5</v>
       </c>
-      <c r="L162" s="27" t="str">
+      <c r="L162" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9102,7 +9115,7 @@
         <f t="shared" si="10"/>
         <v>58</v>
       </c>
-      <c r="L163" s="27" t="str">
+      <c r="L163" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9144,7 +9157,7 @@
         <f t="shared" si="10"/>
         <v>57</v>
       </c>
-      <c r="L164" s="27" t="str">
+      <c r="L164" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9186,7 +9199,7 @@
         <f t="shared" si="10"/>
         <v>56.8</v>
       </c>
-      <c r="L165" s="27" t="str">
+      <c r="L165" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9228,7 +9241,7 @@
         <f t="shared" si="10"/>
         <v>55.96</v>
       </c>
-      <c r="L166" s="27" t="str">
+      <c r="L166" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9270,7 +9283,7 @@
         <f t="shared" si="10"/>
         <v>55.5</v>
       </c>
-      <c r="L167" s="27" t="str">
+      <c r="L167" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9312,7 +9325,7 @@
         <f t="shared" si="10"/>
         <v>55.3</v>
       </c>
-      <c r="L168" s="27" t="str">
+      <c r="L168" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9354,7 +9367,7 @@
         <f t="shared" si="10"/>
         <v>55</v>
       </c>
-      <c r="L169" s="27" t="str">
+      <c r="L169" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9396,7 +9409,7 @@
         <f t="shared" si="10"/>
         <v>55</v>
       </c>
-      <c r="L170" s="27" t="str">
+      <c r="L170" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9438,7 +9451,7 @@
         <f t="shared" si="10"/>
         <v>54</v>
       </c>
-      <c r="L171" s="27" t="str">
+      <c r="L171" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9480,7 +9493,7 @@
         <f t="shared" si="10"/>
         <v>52</v>
       </c>
-      <c r="L172" s="27" t="str">
+      <c r="L172" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9522,7 +9535,7 @@
         <f t="shared" si="10"/>
         <v>51</v>
       </c>
-      <c r="L173" s="27" t="str">
+      <c r="L173" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9564,7 +9577,7 @@
         <f t="shared" si="10"/>
         <v>50.99</v>
       </c>
-      <c r="L174" s="27" t="str">
+      <c r="L174" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9606,7 +9619,7 @@
         <f t="shared" si="10"/>
         <v>50</v>
       </c>
-      <c r="L175" s="27" t="str">
+      <c r="L175" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9648,7 +9661,7 @@
         <f t="shared" si="10"/>
         <v>25</v>
       </c>
-      <c r="L176" s="27" t="str">
+      <c r="L176" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9690,7 +9703,7 @@
         <f t="shared" si="10"/>
         <v>50</v>
       </c>
-      <c r="L177" s="27" t="str">
+      <c r="L177" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9732,7 +9745,7 @@
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
-      <c r="L178" s="27" t="str">
+      <c r="L178" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9774,7 +9787,7 @@
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
-      <c r="L179" s="27" t="str">
+      <c r="L179" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9816,7 +9829,7 @@
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
-      <c r="L180" s="27" t="str">
+      <c r="L180" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9858,7 +9871,7 @@
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
-      <c r="L181" s="27" t="str">
+      <c r="L181" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9900,7 +9913,7 @@
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="L182" s="27" t="str">
+      <c r="L182" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9942,7 +9955,7 @@
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="L183" s="27" t="str">
+      <c r="L183" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9984,7 +9997,7 @@
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
-      <c r="L184" s="27" t="str">
+      <c r="L184" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10026,7 +10039,7 @@
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
-      <c r="L185" s="27" t="str">
+      <c r="L185" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10068,7 +10081,7 @@
         <f t="shared" si="10"/>
         <v>44.75</v>
       </c>
-      <c r="L186" s="27" t="str">
+      <c r="L186" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10110,7 +10123,7 @@
         <f t="shared" si="10"/>
         <v>44</v>
       </c>
-      <c r="L187" s="27" t="str">
+      <c r="L187" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10152,7 +10165,7 @@
         <f t="shared" si="10"/>
         <v>43</v>
       </c>
-      <c r="L188" s="27" t="str">
+      <c r="L188" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10194,7 +10207,7 @@
         <f t="shared" si="10"/>
         <v>42.98</v>
       </c>
-      <c r="L189" s="27" t="str">
+      <c r="L189" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10236,7 +10249,7 @@
         <f t="shared" si="10"/>
         <v>20.245000000000001</v>
       </c>
-      <c r="L190" s="27" t="str">
+      <c r="L190" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10278,7 +10291,7 @@
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="L191" s="27" t="str">
+      <c r="L191" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10320,7 +10333,7 @@
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="L192" s="27" t="str">
+      <c r="L192" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10362,7 +10375,7 @@
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="L193" s="27" t="str">
+      <c r="L193" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10404,7 +10417,7 @@
         <f t="shared" si="10"/>
         <v>39</v>
       </c>
-      <c r="L194" s="27" t="str">
+      <c r="L194" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10435,19 +10448,19 @@
         <v>12.45</v>
       </c>
       <c r="I195" s="22">
-        <f t="shared" ref="I195:I258" si="12">H195/E195</f>
+        <f t="shared" ref="I195:I258" si="12">IF(E195&gt;0, H195/E195, " ")</f>
         <v>0.59285714285714286</v>
       </c>
       <c r="J195" s="22" t="str">
-        <f t="shared" ref="J195:J258" si="13">IF(I195&lt;=0.5,"Low",IF(I195&lt;=1.5,"Medium","High"))</f>
+        <f t="shared" ref="J195:J258" si="13">IF(ISNUMBER(I195), IF(I195&lt;=0.5,"Low",IF(I195&lt;=1.5,"Medium","High")), "UNTESTED ")</f>
         <v>Medium</v>
       </c>
       <c r="K195" s="24">
-        <f t="shared" ref="K195:K258" si="14">G195/F195</f>
+        <f t="shared" ref="K195:K258" si="14">IF(F195&gt;0, G195/F195, " ")</f>
         <v>39</v>
       </c>
-      <c r="L195" s="27" t="str">
-        <f t="shared" ref="L195:L258" si="15">IF(K195&lt;=75,"Low",IF(K195&lt;=200,"Medium","High"))</f>
+      <c r="L195" s="24" t="str">
+        <f t="shared" ref="L195:L258" si="15">IF(ISNUMBER(K195), IF(K195&lt;=75,"Low",IF(K195&lt;=200,"Medium","High")), "Untested")</f>
         <v>Low</v>
       </c>
     </row>
@@ -10488,7 +10501,7 @@
         <f t="shared" si="14"/>
         <v>38.49</v>
       </c>
-      <c r="L196" s="27" t="str">
+      <c r="L196" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10530,7 +10543,7 @@
         <f t="shared" si="14"/>
         <v>38</v>
       </c>
-      <c r="L197" s="27" t="str">
+      <c r="L197" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10572,7 +10585,7 @@
         <f t="shared" si="14"/>
         <v>38</v>
       </c>
-      <c r="L198" s="27" t="str">
+      <c r="L198" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10614,7 +10627,7 @@
         <f t="shared" si="14"/>
         <v>37.5</v>
       </c>
-      <c r="L199" s="27" t="str">
+      <c r="L199" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10656,7 +10669,7 @@
         <f t="shared" si="14"/>
         <v>36.369999999999997</v>
       </c>
-      <c r="L200" s="27" t="str">
+      <c r="L200" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10698,7 +10711,7 @@
         <f t="shared" si="14"/>
         <v>36</v>
       </c>
-      <c r="L201" s="27" t="str">
+      <c r="L201" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10740,7 +10753,7 @@
         <f t="shared" si="14"/>
         <v>35.49</v>
       </c>
-      <c r="L202" s="27" t="str">
+      <c r="L202" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10782,7 +10795,7 @@
         <f t="shared" si="14"/>
         <v>35</v>
       </c>
-      <c r="L203" s="27" t="str">
+      <c r="L203" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10824,7 +10837,7 @@
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
-      <c r="L204" s="27" t="str">
+      <c r="L204" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10866,7 +10879,7 @@
         <f t="shared" si="14"/>
         <v>31.49</v>
       </c>
-      <c r="L205" s="27" t="str">
+      <c r="L205" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10908,7 +10921,7 @@
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
-      <c r="L206" s="27" t="str">
+      <c r="L206" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10950,7 +10963,7 @@
         <f t="shared" si="14"/>
         <v>29</v>
       </c>
-      <c r="L207" s="27" t="str">
+      <c r="L207" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -10992,7 +11005,7 @@
         <f t="shared" si="14"/>
         <v>28</v>
       </c>
-      <c r="L208" s="27" t="str">
+      <c r="L208" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11034,7 +11047,7 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L209" s="27" t="str">
+      <c r="L209" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11076,7 +11089,7 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L210" s="27" t="str">
+      <c r="L210" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11118,7 +11131,7 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L211" s="27" t="str">
+      <c r="L211" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11160,7 +11173,7 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L212" s="27" t="str">
+      <c r="L212" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11202,7 +11215,7 @@
         <f t="shared" si="14"/>
         <v>26</v>
       </c>
-      <c r="L213" s="27" t="str">
+      <c r="L213" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11244,7 +11257,7 @@
         <f t="shared" si="14"/>
         <v>26</v>
       </c>
-      <c r="L214" s="27" t="str">
+      <c r="L214" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11286,7 +11299,7 @@
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L215" s="27" t="str">
+      <c r="L215" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11328,7 +11341,7 @@
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L216" s="27" t="str">
+      <c r="L216" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11370,7 +11383,7 @@
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L217" s="27" t="str">
+      <c r="L217" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11412,7 +11425,7 @@
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L218" s="27" t="str">
+      <c r="L218" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11454,7 +11467,7 @@
         <f t="shared" si="14"/>
         <v>24</v>
       </c>
-      <c r="L219" s="27" t="str">
+      <c r="L219" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11496,7 +11509,7 @@
         <f t="shared" si="14"/>
         <v>23</v>
       </c>
-      <c r="L220" s="27" t="str">
+      <c r="L220" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11538,7 +11551,7 @@
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
-      <c r="L221" s="27" t="str">
+      <c r="L221" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11580,7 +11593,7 @@
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
-      <c r="L222" s="27" t="str">
+      <c r="L222" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11622,7 +11635,7 @@
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
-      <c r="L223" s="27" t="str">
+      <c r="L223" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11664,7 +11677,7 @@
         <f t="shared" si="14"/>
         <v>20.99</v>
       </c>
-      <c r="L224" s="27" t="str">
+      <c r="L224" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11706,7 +11719,7 @@
         <f t="shared" si="14"/>
         <v>18.61</v>
       </c>
-      <c r="L225" s="27" t="str">
+      <c r="L225" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11748,7 +11761,7 @@
         <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="L226" s="27" t="str">
+      <c r="L226" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11790,7 +11803,7 @@
         <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="L227" s="27" t="str">
+      <c r="L227" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11832,7 +11845,7 @@
         <f t="shared" si="14"/>
         <v>17.989999999999998</v>
       </c>
-      <c r="L228" s="27" t="str">
+      <c r="L228" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11874,7 +11887,7 @@
         <f t="shared" si="14"/>
         <v>15.5</v>
       </c>
-      <c r="L229" s="27" t="str">
+      <c r="L229" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11916,7 +11929,7 @@
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="L230" s="27" t="str">
+      <c r="L230" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11958,7 +11971,7 @@
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
-      <c r="L231" s="27" t="str">
+      <c r="L231" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12000,7 +12013,7 @@
         <f t="shared" si="14"/>
         <v>12.5</v>
       </c>
-      <c r="L232" s="27" t="str">
+      <c r="L232" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12042,7 +12055,7 @@
         <f t="shared" si="14"/>
         <v>11.4</v>
       </c>
-      <c r="L233" s="27" t="str">
+      <c r="L233" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12084,7 +12097,7 @@
         <f t="shared" si="14"/>
         <v>8.5</v>
       </c>
-      <c r="L234" s="27" t="str">
+      <c r="L234" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12126,7 +12139,7 @@
         <f t="shared" si="14"/>
         <v>8.5</v>
       </c>
-      <c r="L235" s="27" t="str">
+      <c r="L235" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12168,7 +12181,7 @@
         <f t="shared" si="14"/>
         <v>7.97</v>
       </c>
-      <c r="L236" s="27" t="str">
+      <c r="L236" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12210,7 +12223,7 @@
         <f t="shared" si="14"/>
         <v>7.97</v>
       </c>
-      <c r="L237" s="27" t="str">
+      <c r="L237" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12252,7 +12265,7 @@
         <f t="shared" si="14"/>
         <v>7.8</v>
       </c>
-      <c r="L238" s="27" t="str">
+      <c r="L238" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12294,7 +12307,7 @@
         <f t="shared" si="14"/>
         <v>5.99</v>
       </c>
-      <c r="L239" s="27" t="str">
+      <c r="L239" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12332,13 +12345,13 @@
         <f t="shared" si="13"/>
         <v>Low</v>
       </c>
-      <c r="K240" s="24" t="e">
+      <c r="K240" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L240" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L240" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.2">
@@ -12374,13 +12387,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K241" s="24" t="e">
+      <c r="K241" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L241" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L241" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.2">
@@ -12416,13 +12429,13 @@
         <f t="shared" si="13"/>
         <v>Low</v>
       </c>
-      <c r="K242" s="24" t="e">
+      <c r="K242" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L242" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L242" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.2">
@@ -12458,13 +12471,13 @@
         <f t="shared" si="13"/>
         <v>Low</v>
       </c>
-      <c r="K243" s="24" t="e">
+      <c r="K243" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L243" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L243" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.2">
@@ -12500,13 +12513,13 @@
         <f t="shared" si="13"/>
         <v>High</v>
       </c>
-      <c r="K244" s="24" t="e">
+      <c r="K244" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L244" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L244" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
@@ -12542,13 +12555,13 @@
         <f t="shared" si="13"/>
         <v>Low</v>
       </c>
-      <c r="K245" s="24" t="e">
+      <c r="K245" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L245" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L245" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
@@ -12584,13 +12597,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K246" s="24" t="e">
+      <c r="K246" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L246" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L246" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.2">
@@ -12626,13 +12639,13 @@
         <f t="shared" si="13"/>
         <v>Low</v>
       </c>
-      <c r="K247" s="24" t="e">
+      <c r="K247" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L247" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L247" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.2">
@@ -12668,13 +12681,13 @@
         <f t="shared" si="13"/>
         <v>Low</v>
       </c>
-      <c r="K248" s="24" t="e">
+      <c r="K248" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L248" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L248" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.2">
@@ -12710,13 +12723,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K249" s="24" t="e">
+      <c r="K249" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L249" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L249" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
@@ -12752,13 +12765,13 @@
         <f t="shared" si="13"/>
         <v>Low</v>
       </c>
-      <c r="K250" s="24" t="e">
+      <c r="K250" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L250" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L250" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
@@ -12794,13 +12807,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K251" s="24" t="e">
+      <c r="K251" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L251" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L251" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
@@ -12836,13 +12849,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K252" s="24" t="e">
+      <c r="K252" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L252" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L252" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.2">
@@ -12878,13 +12891,13 @@
         <f t="shared" si="13"/>
         <v>High</v>
       </c>
-      <c r="K253" s="24" t="e">
+      <c r="K253" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L253" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L253" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.2">
@@ -12920,13 +12933,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K254" s="24" t="e">
+      <c r="K254" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L254" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L254" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
@@ -12954,21 +12967,21 @@
       <c r="H255" s="9">
         <v>1.35</v>
       </c>
-      <c r="I255" s="22" t="e">
+      <c r="I255" s="22" t="str">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J255" s="22" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J255" s="22" t="str">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K255" s="24" t="e">
+        <v xml:space="preserve">UNTESTED </v>
+      </c>
+      <c r="K255" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L255" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L255" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
@@ -13004,13 +13017,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K256" s="24" t="e">
+      <c r="K256" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L256" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L256" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.2">
@@ -13046,13 +13059,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K257" s="24" t="e">
+      <c r="K257" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L257" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L257" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.2">
@@ -13088,13 +13101,13 @@
         <f t="shared" si="13"/>
         <v>Medium</v>
       </c>
-      <c r="K258" s="24" t="e">
+      <c r="K258" s="24" t="str">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L258" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L258" s="24" t="str">
         <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.2">
@@ -13123,20 +13136,20 @@
         <v>26.08</v>
       </c>
       <c r="I259" s="22">
-        <f t="shared" ref="I259:I322" si="16">H259/E259</f>
+        <f t="shared" ref="I259:I322" si="16">IF(E259&gt;0, H259/E259, " ")</f>
         <v>1.2419047619047618</v>
       </c>
       <c r="J259" s="22" t="str">
-        <f t="shared" ref="J259:J322" si="17">IF(I259&lt;=0.5,"Low",IF(I259&lt;=1.5,"Medium","High"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="K259" s="24" t="e">
-        <f t="shared" ref="K259:K322" si="18">G259/F259</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L259" s="27" t="e">
-        <f t="shared" ref="L259:L322" si="19">IF(K259&lt;=75,"Low",IF(K259&lt;=200,"Medium","High"))</f>
-        <v>#DIV/0!</v>
+        <f t="shared" ref="J259:J322" si="17">IF(ISNUMBER(I259), IF(I259&lt;=0.5,"Low",IF(I259&lt;=1.5,"Medium","High")), "UNTESTED ")</f>
+        <v>Medium</v>
+      </c>
+      <c r="K259" s="24" t="str">
+        <f t="shared" ref="K259:K322" si="18">IF(F259&gt;0, G259/F259, " ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L259" s="24" t="str">
+        <f t="shared" ref="L259:L322" si="19">IF(ISNUMBER(K259), IF(K259&lt;=75,"Low",IF(K259&lt;=200,"Medium","High")), "Untested")</f>
+        <v>Untested</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.2">
@@ -13172,13 +13185,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K260" s="24" t="e">
+      <c r="K260" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L260" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L260" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.2">
@@ -13214,13 +13227,13 @@
         <f t="shared" si="17"/>
         <v>Low</v>
       </c>
-      <c r="K261" s="24" t="e">
+      <c r="K261" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L261" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L261" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.2">
@@ -13256,13 +13269,13 @@
         <f t="shared" si="17"/>
         <v>Low</v>
       </c>
-      <c r="K262" s="24" t="e">
+      <c r="K262" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L262" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L262" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.2">
@@ -13298,13 +13311,13 @@
         <f t="shared" si="17"/>
         <v>Low</v>
       </c>
-      <c r="K263" s="24" t="e">
+      <c r="K263" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L263" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L263" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.2">
@@ -13340,13 +13353,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K264" s="24" t="e">
+      <c r="K264" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L264" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L264" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.2">
@@ -13382,13 +13395,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K265" s="24" t="e">
+      <c r="K265" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L265" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L265" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.2">
@@ -13416,21 +13429,21 @@
       <c r="H266" s="9">
         <v>3.68</v>
       </c>
-      <c r="I266" s="22" t="e">
+      <c r="I266" s="22" t="str">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J266" s="22" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J266" s="22" t="str">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K266" s="24" t="e">
+        <v xml:space="preserve">UNTESTED </v>
+      </c>
+      <c r="K266" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L266" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L266" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.2">
@@ -13466,13 +13479,13 @@
         <f t="shared" si="17"/>
         <v>Low</v>
       </c>
-      <c r="K267" s="24" t="e">
+      <c r="K267" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L267" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L267" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.2">
@@ -13508,13 +13521,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K268" s="24" t="e">
+      <c r="K268" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L268" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L268" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.2">
@@ -13550,13 +13563,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K269" s="24" t="e">
+      <c r="K269" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L269" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L269" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.2">
@@ -13592,13 +13605,13 @@
         <f t="shared" si="17"/>
         <v>Low</v>
       </c>
-      <c r="K270" s="24" t="e">
+      <c r="K270" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L270" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L270" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.2">
@@ -13634,13 +13647,13 @@
         <f t="shared" si="17"/>
         <v>Low</v>
       </c>
-      <c r="K271" s="24" t="e">
+      <c r="K271" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L271" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L271" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.2">
@@ -13676,13 +13689,13 @@
         <f t="shared" si="17"/>
         <v>Low</v>
       </c>
-      <c r="K272" s="24" t="e">
+      <c r="K272" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L272" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L272" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.2">
@@ -13718,13 +13731,13 @@
         <f t="shared" si="17"/>
         <v>Low</v>
       </c>
-      <c r="K273" s="24" t="e">
+      <c r="K273" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L273" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L273" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.2">
@@ -13760,13 +13773,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K274" s="24" t="e">
+      <c r="K274" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L274" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L274" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.2">
@@ -13802,13 +13815,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K275" s="24" t="e">
+      <c r="K275" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L275" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L275" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.2">
@@ -13844,13 +13857,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K276" s="24" t="e">
+      <c r="K276" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L276" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L276" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.2">
@@ -13886,13 +13899,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K277" s="24" t="e">
+      <c r="K277" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L277" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L277" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.2">
@@ -13928,13 +13941,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K278" s="24" t="e">
+      <c r="K278" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L278" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L278" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.2">
@@ -13970,13 +13983,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K279" s="24" t="e">
+      <c r="K279" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L279" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L279" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.2">
@@ -14012,13 +14025,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K280" s="24" t="e">
+      <c r="K280" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L280" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L280" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.2">
@@ -14054,13 +14067,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K281" s="24" t="e">
+      <c r="K281" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L281" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L281" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.2">
@@ -14096,13 +14109,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K282" s="24" t="e">
+      <c r="K282" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L282" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L282" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.2">
@@ -14138,13 +14151,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K283" s="24" t="e">
+      <c r="K283" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L283" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L283" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.2">
@@ -14180,13 +14193,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K284" s="24" t="e">
+      <c r="K284" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L284" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L284" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.2">
@@ -14222,13 +14235,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K285" s="24" t="e">
+      <c r="K285" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L285" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L285" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.2">
@@ -14264,13 +14277,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K286" s="24" t="e">
+      <c r="K286" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L286" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L286" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.2">
@@ -14306,13 +14319,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K287" s="24" t="e">
+      <c r="K287" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L287" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L287" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.2">
@@ -14348,13 +14361,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K288" s="24" t="e">
+      <c r="K288" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L288" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L288" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.2">
@@ -14390,13 +14403,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K289" s="24" t="e">
+      <c r="K289" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L289" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L289" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.2">
@@ -14432,13 +14445,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K290" s="24" t="e">
+      <c r="K290" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L290" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L290" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.2">
@@ -14474,13 +14487,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K291" s="24" t="e">
+      <c r="K291" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L291" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L291" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.2">
@@ -14516,13 +14529,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K292" s="24" t="e">
+      <c r="K292" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L292" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L292" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.2">
@@ -14558,13 +14571,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K293" s="24" t="e">
+      <c r="K293" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L293" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L293" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.2">
@@ -14600,13 +14613,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K294" s="24" t="e">
+      <c r="K294" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L294" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L294" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.2">
@@ -14642,13 +14655,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K295" s="24" t="e">
+      <c r="K295" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L295" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L295" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.2">
@@ -14684,13 +14697,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K296" s="24" t="e">
+      <c r="K296" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L296" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L296" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.2">
@@ -14726,13 +14739,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K297" s="24" t="e">
+      <c r="K297" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L297" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L297" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.2">
@@ -14768,13 +14781,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K298" s="24" t="e">
+      <c r="K298" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L298" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L298" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.2">
@@ -14810,13 +14823,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K299" s="24" t="e">
+      <c r="K299" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L299" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L299" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.2">
@@ -14852,13 +14865,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K300" s="24" t="e">
+      <c r="K300" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L300" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L300" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.2">
@@ -14894,13 +14907,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K301" s="24" t="e">
+      <c r="K301" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L301" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L301" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.2">
@@ -14936,13 +14949,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K302" s="24" t="e">
+      <c r="K302" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L302" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L302" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.2">
@@ -14978,13 +14991,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K303" s="24" t="e">
+      <c r="K303" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L303" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L303" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.2">
@@ -15020,13 +15033,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K304" s="24" t="e">
+      <c r="K304" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L304" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L304" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.2">
@@ -15062,13 +15075,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K305" s="24" t="e">
+      <c r="K305" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L305" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L305" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.2">
@@ -15104,13 +15117,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K306" s="24" t="e">
+      <c r="K306" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L306" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L306" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.2">
@@ -15146,13 +15159,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K307" s="24" t="e">
+      <c r="K307" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L307" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L307" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.2">
@@ -15188,13 +15201,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K308" s="24" t="e">
+      <c r="K308" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L308" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L308" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.2">
@@ -15230,13 +15243,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K309" s="24" t="e">
+      <c r="K309" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L309" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L309" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.2">
@@ -15272,13 +15285,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K310" s="24" t="e">
+      <c r="K310" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L310" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L310" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.2">
@@ -15314,13 +15327,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K311" s="24" t="e">
+      <c r="K311" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L311" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L311" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.2">
@@ -15356,13 +15369,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K312" s="24" t="e">
+      <c r="K312" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L312" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L312" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.2">
@@ -15398,13 +15411,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K313" s="24" t="e">
+      <c r="K313" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L313" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L313" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.2">
@@ -15440,13 +15453,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K314" s="24" t="e">
+      <c r="K314" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L314" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L314" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.2">
@@ -15482,13 +15495,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K315" s="24" t="e">
+      <c r="K315" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L315" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L315" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.2">
@@ -15524,13 +15537,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K316" s="24" t="e">
+      <c r="K316" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L316" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L316" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.2">
@@ -15566,13 +15579,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K317" s="24" t="e">
+      <c r="K317" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L317" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L317" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.2">
@@ -15608,13 +15621,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K318" s="24" t="e">
+      <c r="K318" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L318" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L318" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.2">
@@ -15650,13 +15663,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K319" s="24" t="e">
+      <c r="K319" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L319" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L319" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.2">
@@ -15692,13 +15705,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K320" s="24" t="e">
+      <c r="K320" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L320" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L320" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.2">
@@ -15734,13 +15747,13 @@
         <f t="shared" si="17"/>
         <v>Medium</v>
       </c>
-      <c r="K321" s="24" t="e">
+      <c r="K321" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L321" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L321" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.2">
@@ -15776,13 +15789,13 @@
         <f t="shared" si="17"/>
         <v>High</v>
       </c>
-      <c r="K322" s="24" t="e">
+      <c r="K322" s="24" t="str">
         <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L322" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L322" s="24" t="str">
         <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.2">
@@ -15811,20 +15824,20 @@
         <v>37.65</v>
       </c>
       <c r="I323" s="22">
-        <f t="shared" ref="I323:I381" si="20">H323/E323</f>
+        <f t="shared" ref="I323:I381" si="20">IF(E323&gt;0, H323/E323, " ")</f>
         <v>1.344642857142857</v>
       </c>
       <c r="J323" s="22" t="str">
-        <f t="shared" ref="J323:J381" si="21">IF(I323&lt;=0.5,"Low",IF(I323&lt;=1.5,"Medium","High"))</f>
-        <v>Medium</v>
-      </c>
-      <c r="K323" s="24" t="e">
-        <f t="shared" ref="K323:K381" si="22">G323/F323</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L323" s="27" t="e">
-        <f t="shared" ref="L323:L381" si="23">IF(K323&lt;=75,"Low",IF(K323&lt;=200,"Medium","High"))</f>
-        <v>#DIV/0!</v>
+        <f t="shared" ref="J323:J381" si="21">IF(ISNUMBER(I323), IF(I323&lt;=0.5,"Low",IF(I323&lt;=1.5,"Medium","High")), "UNTESTED ")</f>
+        <v>Medium</v>
+      </c>
+      <c r="K323" s="24" t="str">
+        <f t="shared" ref="K323:K381" si="22">IF(F323&gt;0, G323/F323, " ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L323" s="24" t="str">
+        <f t="shared" ref="L323:L381" si="23">IF(ISNUMBER(K323), IF(K323&lt;=75,"Low",IF(K323&lt;=200,"Medium","High")), "Untested")</f>
+        <v>Untested</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.2">
@@ -15860,13 +15873,13 @@
         <f t="shared" si="21"/>
         <v>Low</v>
       </c>
-      <c r="K324" s="24" t="e">
+      <c r="K324" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L324" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L324" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.2">
@@ -15894,21 +15907,21 @@
       <c r="H325" s="9">
         <v>1.63</v>
       </c>
-      <c r="I325" s="22" t="e">
+      <c r="I325" s="22" t="str">
         <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J325" s="22" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J325" s="22" t="str">
         <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K325" s="24" t="e">
+        <v xml:space="preserve">UNTESTED </v>
+      </c>
+      <c r="K325" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L325" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L325" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.2">
@@ -15944,13 +15957,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K326" s="24" t="e">
+      <c r="K326" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L326" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L326" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.2">
@@ -15986,13 +15999,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K327" s="24" t="e">
+      <c r="K327" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L327" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L327" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.2">
@@ -16028,13 +16041,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K328" s="24" t="e">
+      <c r="K328" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L328" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L328" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.2">
@@ -16070,13 +16083,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K329" s="24" t="e">
+      <c r="K329" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L329" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L329" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.2">
@@ -16112,13 +16125,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K330" s="24" t="e">
+      <c r="K330" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L330" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L330" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.2">
@@ -16154,13 +16167,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K331" s="24" t="e">
+      <c r="K331" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L331" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L331" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.2">
@@ -16196,13 +16209,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K332" s="24" t="e">
+      <c r="K332" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L332" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L332" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.2">
@@ -16238,13 +16251,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K333" s="24" t="e">
+      <c r="K333" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L333" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L333" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.2">
@@ -16280,13 +16293,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K334" s="24" t="e">
+      <c r="K334" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L334" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L334" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.2">
@@ -16322,13 +16335,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K335" s="24" t="e">
+      <c r="K335" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L335" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L335" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.2">
@@ -16364,13 +16377,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K336" s="24" t="e">
+      <c r="K336" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L336" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L336" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.2">
@@ -16406,13 +16419,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K337" s="24" t="e">
+      <c r="K337" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L337" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L337" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.2">
@@ -16448,13 +16461,13 @@
         <f t="shared" si="21"/>
         <v>Low</v>
       </c>
-      <c r="K338" s="24" t="e">
+      <c r="K338" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L338" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L338" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.2">
@@ -16490,13 +16503,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K339" s="24" t="e">
+      <c r="K339" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L339" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L339" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.2">
@@ -16532,13 +16545,13 @@
         <f t="shared" si="21"/>
         <v>Low</v>
       </c>
-      <c r="K340" s="24" t="e">
+      <c r="K340" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L340" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L340" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.2">
@@ -16574,13 +16587,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K341" s="24" t="e">
+      <c r="K341" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L341" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L341" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.2">
@@ -16616,13 +16629,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K342" s="24" t="e">
+      <c r="K342" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L342" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L342" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.2">
@@ -16658,13 +16671,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K343" s="24" t="e">
+      <c r="K343" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L343" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L343" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.2">
@@ -16700,13 +16713,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K344" s="24" t="e">
+      <c r="K344" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L344" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L344" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.2">
@@ -16742,13 +16755,13 @@
         <f t="shared" si="21"/>
         <v>Low</v>
       </c>
-      <c r="K345" s="24" t="e">
+      <c r="K345" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L345" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L345" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.2">
@@ -16784,13 +16797,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K346" s="24" t="e">
+      <c r="K346" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L346" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L346" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.2">
@@ -16826,13 +16839,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K347" s="24" t="e">
+      <c r="K347" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L347" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L347" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.2">
@@ -16868,13 +16881,13 @@
         <f t="shared" si="21"/>
         <v>Low</v>
       </c>
-      <c r="K348" s="24" t="e">
+      <c r="K348" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L348" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L348" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.2">
@@ -16910,13 +16923,13 @@
         <f t="shared" si="21"/>
         <v>Low</v>
       </c>
-      <c r="K349" s="24" t="e">
+      <c r="K349" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L349" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L349" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.2">
@@ -16952,13 +16965,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K350" s="24" t="e">
+      <c r="K350" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L350" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L350" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.2">
@@ -16994,13 +17007,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K351" s="24" t="e">
+      <c r="K351" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L351" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L351" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.2">
@@ -17036,13 +17049,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K352" s="24" t="e">
+      <c r="K352" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L352" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L352" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.2">
@@ -17078,13 +17091,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K353" s="24" t="e">
+      <c r="K353" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L353" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L353" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.2">
@@ -17120,13 +17133,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K354" s="24" t="e">
+      <c r="K354" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L354" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L354" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.2">
@@ -17162,13 +17175,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K355" s="24" t="e">
+      <c r="K355" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L355" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L355" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.2">
@@ -17204,13 +17217,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K356" s="24" t="e">
+      <c r="K356" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L356" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L356" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.2">
@@ -17246,13 +17259,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K357" s="24" t="e">
+      <c r="K357" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L357" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L357" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.2">
@@ -17288,13 +17301,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K358" s="24" t="e">
+      <c r="K358" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L358" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L358" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.2">
@@ -17330,13 +17343,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K359" s="24" t="e">
+      <c r="K359" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L359" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L359" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.2">
@@ -17372,13 +17385,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K360" s="24" t="e">
+      <c r="K360" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L360" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L360" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.2">
@@ -17414,13 +17427,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K361" s="24" t="e">
+      <c r="K361" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L361" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L361" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.2">
@@ -17456,13 +17469,13 @@
         <f t="shared" si="21"/>
         <v>Low</v>
       </c>
-      <c r="K362" s="24" t="e">
+      <c r="K362" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L362" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L362" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.2">
@@ -17498,13 +17511,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K363" s="24" t="e">
+      <c r="K363" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L363" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L363" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.2">
@@ -17540,13 +17553,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K364" s="24" t="e">
+      <c r="K364" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L364" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L364" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.2">
@@ -17582,13 +17595,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K365" s="24" t="e">
+      <c r="K365" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L365" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L365" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.2">
@@ -17624,13 +17637,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K366" s="24" t="e">
+      <c r="K366" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L366" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L366" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.2">
@@ -17666,13 +17679,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K367" s="24" t="e">
+      <c r="K367" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L367" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L367" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.2">
@@ -17708,13 +17721,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K368" s="24" t="e">
+      <c r="K368" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L368" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L368" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.2">
@@ -17750,13 +17763,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K369" s="24" t="e">
+      <c r="K369" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L369" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L369" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.2">
@@ -17792,13 +17805,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K370" s="24" t="e">
+      <c r="K370" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L370" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L370" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.2">
@@ -17834,13 +17847,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K371" s="24" t="e">
+      <c r="K371" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L371" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L371" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.2">
@@ -17876,13 +17889,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K372" s="24" t="e">
+      <c r="K372" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L372" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L372" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.2">
@@ -17918,13 +17931,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K373" s="24" t="e">
+      <c r="K373" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L373" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L373" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.2">
@@ -17960,13 +17973,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K374" s="24" t="e">
+      <c r="K374" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L374" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L374" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.2">
@@ -18002,13 +18015,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K375" s="24" t="e">
+      <c r="K375" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L375" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L375" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.2">
@@ -18044,13 +18057,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K376" s="24" t="e">
+      <c r="K376" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L376" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L376" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.2">
@@ -18086,13 +18099,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K377" s="24" t="e">
+      <c r="K377" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L377" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L377" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.2">
@@ -18128,13 +18141,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K378" s="24" t="e">
+      <c r="K378" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L378" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L378" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.2">
@@ -18170,13 +18183,13 @@
         <f t="shared" si="21"/>
         <v>High</v>
       </c>
-      <c r="K379" s="24" t="e">
+      <c r="K379" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L379" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L379" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.2">
@@ -18212,13 +18225,13 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K380" s="24" t="e">
+      <c r="K380" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L380" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L380" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.2">
@@ -18254,17 +18267,17 @@
         <f t="shared" si="21"/>
         <v>Medium</v>
       </c>
-      <c r="K381" s="24" t="e">
+      <c r="K381" s="24" t="str">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L381" s="27" t="e">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="L381" s="24" t="str">
         <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
+        <v>Untested</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:H383">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H383">
     <sortCondition descending="1" ref="G2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18272,7 +18285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -18335,7 +18348,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="28" t="s">
         <v>401</v>
       </c>
       <c r="B4" s="12" t="s">
@@ -18372,7 +18385,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="30"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="12" t="s">
         <v>237</v>
       </c>
@@ -18413,7 +18426,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="12" t="s">
         <v>22</v>
       </c>
@@ -18452,7 +18465,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="30"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="12" t="s">
         <v>388</v>
       </c>
@@ -18487,7 +18500,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="30"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="12" t="s">
         <v>386</v>
       </c>
@@ -18530,7 +18543,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="30"/>
+      <c r="A9" s="28"/>
       <c r="B9" s="12" t="s">
         <v>400</v>
       </c>
